--- a/InputData/elec/LFHVM/Load Factor Hourly Variance Multiplier.xlsx
+++ b/InputData/elec/LFHVM/Load Factor Hourly Variance Multiplier.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\NM\elec\LFHVM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0128DE82-A33F-452B-9350-03CF3AEF1E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10BB269A-658F-431B-B84E-BC4C8E93F4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{E755D2B6-154D-4132-AE62-7719D42AA9EA}"/>
+    <workbookView xWindow="1690" yWindow="720" windowWidth="14480" windowHeight="10080" xr2:uid="{E755D2B6-154D-4132-AE62-7719D42AA9EA}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -552,12 +552,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AFABDF-6A59-4ED9-8641-463A0343EC57}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="43.1328125" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,10 +565,10 @@
         <v>38</v>
       </c>
       <c r="C1" s="8">
-        <v>45237</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -576,67 +576,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -656,13 +656,13 @@
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.40625" customWidth="1"/>
-    <col min="2" max="9" width="16.26953125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="2" max="9" width="16.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>37</v>
       </c>
@@ -691,7 +691,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -720,7 +720,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -749,7 +749,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -778,7 +778,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -807,7 +807,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -836,7 +836,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -865,7 +865,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -894,7 +894,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -923,7 +923,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -952,7 +952,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -981,7 +981,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
